--- a/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
@@ -7,7 +7,8 @@
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Variables dicotomizadas" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Porcentajes" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Totales" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -526,7 +527,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a</t>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -716,17 +717,17 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
@@ -736,37 +737,37 @@
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>0; 12,61</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>0; 36,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0; 56,93</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>0; 10,53</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>0; 5,96</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -856,52 +857,52 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,97</t>
+          <t>0,0; 29,64</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>0; 7,06</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>0; 26,42</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,03; 47,47</t>
+          <t>12,41; 46,75</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,4; 20,51</t>
+          <t>2,36; 18,77</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,19</t>
+          <t>0,0; 40,23</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,11; 32,21</t>
+          <t>9,52; 33,69</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,4</t>
+          <t>1,44; 12,25</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
@@ -911,7 +912,7 @@
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>0; 13,49</t>
+          <t>—; —</t>
         </is>
       </c>
     </row>
@@ -996,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,54</t>
+          <t>0,0; 44,68</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,99</t>
+          <t>0,0; 33,57</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>0; 17,08</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>0; 23,25</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,54</t>
+          <t>0,0; 38,12</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 39,87</t>
+          <t>0,0; 43,42</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,76</t>
+          <t>0,0; 35,1</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 74,4</t>
+          <t>0,0; 75,05</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 26,95</t>
+          <t>2,65; 25,68</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,67; 29,83</t>
+          <t>2,71; 29,69</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,87</t>
+          <t>0,0; 25,44</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 55,13</t>
+          <t>0,0; 51,59</t>
         </is>
       </c>
     </row>
@@ -1136,62 +1137,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,5</t>
+          <t>0,0; 41,7</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
+          <t>0,0; 34,19</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0,0; 50,8</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>0,0; 35,42</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0; 12,61</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 48,47</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>0,0; 34,83</t>
-        </is>
-      </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,69; 29,49</t>
+          <t>5,62; 30,73</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>0; 9,05</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>0; 15,69</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,42; 28,14</t>
+          <t>3,26; 26,65</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,65; 24,82</t>
+          <t>6,25; 24,1</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>0; 5,45</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,69</t>
+          <t>0,0; 24,64</t>
         </is>
       </c>
     </row>
@@ -1276,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,73; 21,0</t>
+          <t>3,65; 20,14</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 11,3</t>
+          <t>1,18; 13,01</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>0; 5,16</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 27,83</t>
+          <t>0,0; 30,62</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,39; 24,22</t>
+          <t>7,41; 24,96</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>4,76; 17,17</t>
+          <t>5,37; 16,43</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,81; 17,83</t>
+          <t>1,75; 16,83</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,69</t>
+          <t>0,0; 31,1</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,69; 19,83</t>
+          <t>7,75; 19,44</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,57; 12,31</t>
+          <t>4,35; 12,46</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,15; 10,88</t>
+          <t>1,51; 11,85</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,22; 24,39</t>
+          <t>3,24; 23,58</t>
         </is>
       </c>
     </row>
@@ -1356,4 +1357,1204 @@
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
+</file>
+
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:N19"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <cols>
+    <col width="14" customWidth="1" min="1" max="1"/>
+    <col width="14" customWidth="1" min="2" max="2"/>
+    <col width="14" customWidth="1" min="3" max="3"/>
+    <col width="14" customWidth="1" min="4" max="4"/>
+    <col width="14" customWidth="1" min="5" max="5"/>
+    <col width="14" customWidth="1" min="6" max="6"/>
+    <col width="14" customWidth="1" min="7" max="7"/>
+    <col width="14" customWidth="1" min="8" max="8"/>
+    <col width="14" customWidth="1" min="9" max="9"/>
+    <col width="14" customWidth="1" min="10" max="10"/>
+    <col width="14" customWidth="1" min="11" max="11"/>
+    <col width="14" customWidth="1" min="12" max="12"/>
+    <col width="14" customWidth="1" min="13" max="13"/>
+    <col width="14" customWidth="1" min="14" max="14"/>
+  </cols>
+  <sheetData>
+    <row r="1">
+      <c r="A1" s="1" t="inlineStr">
+        <is>
+          <t>Menores que a consecuencia del accidente necesitaron asistencia sanitaria y consultaron a un médico/a o enfermero/a (tasa de respuesta: 100,0%)</t>
+        </is>
+      </c>
+      <c r="B1" s="2" t="n"/>
+      <c r="C1" s="3" t="inlineStr">
+        <is>
+          <t>Niña</t>
+        </is>
+      </c>
+      <c r="D1" s="3" t="n"/>
+      <c r="E1" s="3" t="n"/>
+      <c r="F1" s="3" t="n"/>
+      <c r="G1" s="3" t="inlineStr">
+        <is>
+          <t>Niño</t>
+        </is>
+      </c>
+      <c r="H1" s="3" t="n"/>
+      <c r="I1" s="3" t="n"/>
+      <c r="J1" s="3" t="n"/>
+      <c r="K1" s="3" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="L1" s="3" t="n"/>
+      <c r="M1" s="3" t="n"/>
+      <c r="N1" s="3" t="n"/>
+    </row>
+    <row r="2">
+      <c r="A2" s="4" t="n"/>
+      <c r="B2" s="2" t="n"/>
+      <c r="C2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="D2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="E2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="F2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="G2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="H2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="I2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="J2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="K2" s="3" t="inlineStr">
+        <is>
+          <t>2007</t>
+        </is>
+      </c>
+      <c r="L2" s="3" t="inlineStr">
+        <is>
+          <t>2012</t>
+        </is>
+      </c>
+      <c r="M2" s="3" t="inlineStr">
+        <is>
+          <t>2016</t>
+        </is>
+      </c>
+      <c r="N2" s="3" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+    </row>
+    <row r="3" hidden="1">
+      <c r="A3" s="4" t="n"/>
+      <c r="B3" s="2" t="n"/>
+      <c r="C3" s="2" t="n"/>
+      <c r="D3" s="2" t="n"/>
+      <c r="E3" s="2" t="n"/>
+      <c r="F3" s="2" t="n"/>
+      <c r="G3" s="2" t="n"/>
+      <c r="H3" s="2" t="n"/>
+      <c r="I3" s="2" t="n"/>
+      <c r="J3" s="2" t="n"/>
+      <c r="K3" s="2" t="n"/>
+      <c r="L3" s="2" t="n"/>
+      <c r="M3" s="2" t="n"/>
+      <c r="N3" s="2" t="n"/>
+    </row>
+    <row r="4">
+      <c r="A4" s="1" t="inlineStr">
+        <is>
+          <t>0-2</t>
+        </is>
+      </c>
+      <c r="B4" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N4" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="1" t="n"/>
+      <c r="B5" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F5" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="M5" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N5" s="2" t="inlineStr">
+        <is>
+          <t>408</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="1" t="n"/>
+      <c r="B6" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0; 758</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="L6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="M6" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N6" s="2" t="inlineStr">
+        <is>
+          <t>0; 1629</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="1" t="inlineStr">
+        <is>
+          <t>3-7</t>
+        </is>
+      </c>
+      <c r="B7" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="H7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="I7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K7" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="L7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M7" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N7" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" s="1" t="n"/>
+      <c r="B8" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C8" s="2" t="inlineStr">
+        <is>
+          <t>1292</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="H8" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="I8" s="2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="J8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K8" s="2" t="inlineStr">
+        <is>
+          <t>5493</t>
+        </is>
+      </c>
+      <c r="L8" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="M8" s="2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="N8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" s="1" t="n"/>
+      <c r="B9" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C9" s="2" t="inlineStr">
+        <is>
+          <t>0; 3961</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="E9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G9" s="2" t="inlineStr">
+        <is>
+          <t>1994; 7509</t>
+        </is>
+      </c>
+      <c r="H9" s="2" t="inlineStr">
+        <is>
+          <t>666; 5302</t>
+        </is>
+      </c>
+      <c r="I9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4578</t>
+        </is>
+      </c>
+      <c r="J9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K9" s="2" t="inlineStr">
+        <is>
+          <t>2802; 9911</t>
+        </is>
+      </c>
+      <c r="L9" s="2" t="inlineStr">
+        <is>
+          <t>671; 5721</t>
+        </is>
+      </c>
+      <c r="M9" s="2" t="inlineStr">
+        <is>
+          <t>0; 4695</t>
+        </is>
+      </c>
+      <c r="N9" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" s="1" t="inlineStr">
+        <is>
+          <t>8-11</t>
+        </is>
+      </c>
+      <c r="B10" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="N10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" s="1" t="n"/>
+      <c r="B11" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C11" s="2" t="inlineStr">
+        <is>
+          <t>806</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>930</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="H11" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="I11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="N11" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" s="1" t="n"/>
+      <c r="B12" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3929</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>0; 3618</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4216</t>
+        </is>
+      </c>
+      <c r="H12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5410</t>
+        </is>
+      </c>
+      <c r="I12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4279</t>
+        </is>
+      </c>
+      <c r="J12" s="2" t="inlineStr">
+        <is>
+          <t>0; 5780</t>
+        </is>
+      </c>
+      <c r="K12" s="2" t="inlineStr">
+        <is>
+          <t>526; 5098</t>
+        </is>
+      </c>
+      <c r="L12" s="2" t="inlineStr">
+        <is>
+          <t>630; 6898</t>
+        </is>
+      </c>
+      <c r="M12" s="2" t="inlineStr">
+        <is>
+          <t>0; 4696</t>
+        </is>
+      </c>
+      <c r="N12" s="2" t="inlineStr">
+        <is>
+          <t>0; 6490</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" s="1" t="inlineStr">
+        <is>
+          <t>12-15</t>
+        </is>
+      </c>
+      <c r="B13" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K13" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="L13" s="2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="M13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N13" s="2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" s="1" t="n"/>
+      <c r="B14" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C14" s="2" t="inlineStr">
+        <is>
+          <t>1324</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>1306</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="H14" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="I14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K14" s="2" t="inlineStr">
+        <is>
+          <t>2789</t>
+        </is>
+      </c>
+      <c r="L14" s="2" t="inlineStr">
+        <is>
+          <t>4785</t>
+        </is>
+      </c>
+      <c r="M14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="N14" s="2" t="inlineStr">
+        <is>
+          <t>994</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" s="1" t="n"/>
+      <c r="B15" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4011</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4019</t>
+        </is>
+      </c>
+      <c r="E15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F15" s="2" t="inlineStr">
+        <is>
+          <t>0; 3961</t>
+        </is>
+      </c>
+      <c r="G15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4382</t>
+        </is>
+      </c>
+      <c r="H15" s="2" t="inlineStr">
+        <is>
+          <t>1320; 7212</t>
+        </is>
+      </c>
+      <c r="I15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="K15" s="2" t="inlineStr">
+        <is>
+          <t>717; 5858</t>
+        </is>
+      </c>
+      <c r="L15" s="2" t="inlineStr">
+        <is>
+          <t>2200; 8488</t>
+        </is>
+      </c>
+      <c r="M15" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="N15" s="2" t="inlineStr">
+        <is>
+          <t>0; 4247</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" s="1" t="inlineStr">
+        <is>
+          <t>Total</t>
+        </is>
+      </c>
+      <c r="B16" s="3" t="inlineStr">
+        <is>
+          <t>n</t>
+        </is>
+      </c>
+      <c r="C16" s="2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="I16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="J16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="K16" s="2" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="L16" s="2" t="inlineStr">
+        <is>
+          <t>14</t>
+        </is>
+      </c>
+      <c r="M16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="N16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" s="1" t="n"/>
+      <c r="B17" s="3" t="inlineStr">
+        <is>
+          <t>N (estimada)</t>
+        </is>
+      </c>
+      <c r="C17" s="2" t="inlineStr">
+        <is>
+          <t>3422</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>2236</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>1402</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="H17" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="I17" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>2439</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="N17" s="2" t="inlineStr">
+        <is>
+          <t>3841</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" s="1" t="n"/>
+      <c r="B18" s="3" t="inlineStr">
+        <is>
+          <t>IC 95%</t>
+        </is>
+      </c>
+      <c r="C18" s="2" t="inlineStr">
+        <is>
+          <t>1290; 7111</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
+          <t>610; 6728</t>
+        </is>
+      </c>
+      <c r="E18" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="F18" s="2" t="inlineStr">
+        <is>
+          <t>0; 5252</t>
+        </is>
+      </c>
+      <c r="G18" s="2" t="inlineStr">
+        <is>
+          <t>3448; 11613</t>
+        </is>
+      </c>
+      <c r="H18" s="2" t="inlineStr">
+        <is>
+          <t>3937; 12053</t>
+        </is>
+      </c>
+      <c r="I18" s="2" t="inlineStr">
+        <is>
+          <t>715; 6852</t>
+        </is>
+      </c>
+      <c r="J18" s="2" t="inlineStr">
+        <is>
+          <t>0; 7475</t>
+        </is>
+      </c>
+      <c r="K18" s="2" t="inlineStr">
+        <is>
+          <t>6338; 15907</t>
+        </is>
+      </c>
+      <c r="L18" s="2" t="inlineStr">
+        <is>
+          <t>5443; 15581</t>
+        </is>
+      </c>
+      <c r="M18" s="2" t="inlineStr">
+        <is>
+          <t>967; 7594</t>
+        </is>
+      </c>
+      <c r="N18" s="2" t="inlineStr">
+        <is>
+          <t>1334; 9712</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>Fuente: Encuesta Andaluza de Salud (menores)</t>
+        </is>
+      </c>
+    </row>
+  </sheetData>
+  <mergeCells count="9">
+    <mergeCell ref="A7:A9"/>
+    <mergeCell ref="A4:A6"/>
+    <mergeCell ref="A16:A18"/>
+    <mergeCell ref="A10:A12"/>
+    <mergeCell ref="A1:B2"/>
+    <mergeCell ref="C1:F1"/>
+    <mergeCell ref="G1:J1"/>
+    <mergeCell ref="K1:N1"/>
+    <mergeCell ref="A13:A15"/>
+  </mergeCells>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
 </file>
--- a/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
@@ -857,7 +857,7 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,64</t>
+          <t>0,0; 34,87</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,41; 46,75</t>
+          <t>12,29; 47,33</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,36; 18,77</t>
+          <t>2,39; 21,27</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,23</t>
+          <t>0,0; 40,83</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>9,52; 33,69</t>
+          <t>8,42; 32,47</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,25</t>
+          <t>1,44; 12,56</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 26,49</t>
+          <t>0,0; 30,83</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -997,12 +997,12 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 44,68</t>
+          <t>0,0; 36,28</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,57</t>
+          <t>0,0; 40,34</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
@@ -1017,42 +1017,42 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 38,12</t>
+          <t>0,0; 34,48</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 43,42</t>
+          <t>0,0; 42,53</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,1</t>
+          <t>0,0; 35,37</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 75,05</t>
+          <t>0,0; 77,37</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,65; 25,68</t>
+          <t>2,64; 26,57</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,71; 29,69</t>
+          <t>2,54; 27,19</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 25,44</t>
+          <t>0,0; 24,04</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 51,59</t>
+          <t>0,0; 50,38</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 41,7</t>
+          <t>0,0; 40,84</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,19</t>
+          <t>0,0; 33,15</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,8</t>
+          <t>0,0; 54,14</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,42</t>
+          <t>0,0; 35,37</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>5,62; 30,73</t>
+          <t>6,84; 29,69</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1177,12 +1177,12 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>3,26; 26,65</t>
+          <t>2,98; 28,22</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,25; 24,1</t>
+          <t>6,73; 25,17</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,64</t>
+          <t>0,0; 28,75</t>
         </is>
       </c>
     </row>
@@ -1277,12 +1277,12 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,65; 20,14</t>
+          <t>3,64; 21,26</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,18; 13,01</t>
+          <t>1,17; 11,81</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
@@ -1292,47 +1292,47 @@
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,62</t>
+          <t>0,0; 30,43</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,41; 24,96</t>
+          <t>7,67; 25,53</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,37; 16,43</t>
+          <t>5,31; 16,95</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,75; 16,83</t>
+          <t>1,82; 17,13</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 31,1</t>
+          <t>0,0; 29,46</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,75; 19,44</t>
+          <t>7,71; 20,07</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,35; 12,46</t>
+          <t>4,53; 12,98</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,51; 11,85</t>
+          <t>1,53; 10,81</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>3,24; 23,58</t>
+          <t>2,53; 24,69</t>
         </is>
       </c>
     </row>
@@ -1853,7 +1853,7 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 3961</t>
+          <t>0; 4659</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
@@ -1873,17 +1873,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1994; 7509</t>
+          <t>1973; 7602</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>666; 5302</t>
+          <t>675; 6006</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4578</t>
+          <t>0; 4646</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2802; 9911</t>
+          <t>2478; 9555</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671; 5721</t>
+          <t>671; 5869</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 4695</t>
+          <t>0; 5464</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -2061,12 +2061,12 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3929</t>
+          <t>0; 3191</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 3618</t>
+          <t>0; 4347</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
@@ -2081,42 +2081,42 @@
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 4216</t>
+          <t>0; 3813</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5410</t>
+          <t>0; 5299</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4279</t>
+          <t>0; 4312</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5780</t>
+          <t>0; 5959</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>526; 5098</t>
+          <t>524; 5275</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>630; 6898</t>
+          <t>589; 6316</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4696</t>
+          <t>0; 4438</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6490</t>
+          <t>0; 6338</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 4011</t>
+          <t>0; 3928</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 4019</t>
+          <t>0; 3896</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 3961</t>
+          <t>0; 4222</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4382</t>
+          <t>0; 4375</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1320; 7212</t>
+          <t>1606; 6968</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2309,12 +2309,12 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>717; 5858</t>
+          <t>656; 6205</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2200; 8488</t>
+          <t>2370; 8868</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4247</t>
+          <t>0; 4954</t>
         </is>
       </c>
     </row>
@@ -2477,12 +2477,12 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1290; 7111</t>
+          <t>1284; 7505</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>610; 6728</t>
+          <t>607; 6107</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
@@ -2492,47 +2492,47 @@
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5252</t>
+          <t>0; 5219</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3448; 11613</t>
+          <t>3566; 11877</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3937; 12053</t>
+          <t>3899; 12435</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>715; 6852</t>
+          <t>741; 6975</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 7475</t>
+          <t>0; 7081</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6338; 15907</t>
+          <t>6305; 16421</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5443; 15581</t>
+          <t>5667; 16233</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>967; 7594</t>
+          <t>980; 6928</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1334; 9712</t>
+          <t>1042; 10170</t>
         </is>
       </c>
     </row>

--- a/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
+++ b/data/trans_dic/IP11C$medico-Edad-trans_dic.xlsx
@@ -533,7 +533,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -541,7 +541,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -664,7 +664,7 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>53,8%</t>
+          <t>0,0%</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -684,27 +684,27 @@
       </c>
       <c r="J4" s="2" t="inlineStr">
         <is>
+          <t>54,46%</t>
+        </is>
+      </c>
+      <c r="K4" s="2" t="inlineStr">
+        <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="K4" s="2" t="inlineStr">
+      <c r="L4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="L4" s="2" t="inlineStr">
+      <c r="M4" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="M4" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>19,47%</t>
+          <t>17,55%</t>
         </is>
       </c>
     </row>
@@ -732,29 +732,29 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="G5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="H5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="I5" s="2" t="inlineStr">
+        <is>
+          <t>—; —</t>
+        </is>
+      </c>
+      <c r="J5" s="2" t="inlineStr">
+        <is>
           <t>0,0; 100,0</t>
         </is>
       </c>
-      <c r="G5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="H5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="I5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
-      <c r="J5" s="2" t="inlineStr">
-        <is>
-          <t>—; —</t>
-        </is>
-      </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
           <t>—; —</t>
@@ -772,7 +772,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,75</t>
+          <t>0,0; 78,2</t>
         </is>
       </c>
     </row>
@@ -789,37 +789,37 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>26,16%</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
+          <t>7,66%</t>
+        </is>
+      </c>
+      <c r="E6" s="2" t="inlineStr">
+        <is>
+          <t>14,15%</t>
+        </is>
+      </c>
+      <c r="F6" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G6" s="2" t="inlineStr">
+        <is>
           <t>9,67%</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="H6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="I6" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
-        </is>
-      </c>
-      <c r="F6" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="G6" s="2" t="inlineStr">
-        <is>
-          <t>26,16%</t>
-        </is>
-      </c>
-      <c r="H6" s="2" t="inlineStr">
-        <is>
-          <t>7,66%</t>
-        </is>
-      </c>
-      <c r="I6" s="2" t="inlineStr">
-        <is>
-          <t>14,15%</t>
         </is>
       </c>
       <c r="J6" s="2" t="inlineStr">
@@ -857,17 +857,17 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,87</t>
+          <t>12,03; 47,47</t>
         </is>
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>2,4; 20,51</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 41,19</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
@@ -877,17 +877,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>12,29; 47,33</t>
+          <t>0,0; 30,97</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>2,39; 21,27</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,83</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -897,17 +897,17 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>8,42; 32,47</t>
+          <t>9,11; 32,21</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>1,44; 12,56</t>
+          <t>1,44; 12,4</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,83</t>
+          <t>0,0; 26,49</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -929,44 +929,44 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>11,06%</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>13,79%</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>11,72%</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>33,01%</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>9,16%</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="H8" s="2" t="inlineStr">
         <is>
           <t>8,63%</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="I8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr">
+      <c r="J8" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>11,06%</t>
-        </is>
-      </c>
-      <c r="H8" s="2" t="inlineStr">
-        <is>
-          <t>13,79%</t>
-        </is>
-      </c>
-      <c r="I8" s="2" t="inlineStr">
-        <is>
-          <t>11,72%</t>
-        </is>
-      </c>
-      <c r="J8" s="2" t="inlineStr">
-        <is>
-          <t>31,67%</t>
-        </is>
-      </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
           <t>10,22%</t>
@@ -984,7 +984,7 @@
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>19,39%</t>
+          <t>19,95%</t>
         </is>
       </c>
     </row>
@@ -997,62 +997,62 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 36,28</t>
+          <t>0,0; 30,54</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,34</t>
+          <t>0,0; 39,87</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 30,76</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 75,63</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 34,48</t>
+          <t>0,0; 42,54</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 42,53</t>
+          <t>0,0; 39,99</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 77,37</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2,64; 26,57</t>
+          <t>2,67; 26,95</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>2,54; 27,19</t>
+          <t>2,67; 29,83</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 24,04</t>
+          <t>0,0; 27,87</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
         <is>
-          <t>0,0; 50,38</t>
+          <t>0,0; 56,46</t>
         </is>
       </c>
     </row>
@@ -1069,62 +1069,62 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>11,85%</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>14,82%</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>0,0%</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>13,76%</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>11,11%</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="I10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>12,75%</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>11,85%</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>14,82%</t>
-        </is>
-      </c>
-      <c r="I10" s="2" t="inlineStr">
+      <c r="J10" s="2" t="inlineStr">
+        <is>
+          <t>12,18%</t>
+        </is>
+      </c>
+      <c r="K10" s="2" t="inlineStr">
+        <is>
+          <t>12,69%</t>
+        </is>
+      </c>
+      <c r="L10" s="2" t="inlineStr">
+        <is>
+          <t>13,58%</t>
+        </is>
+      </c>
+      <c r="M10" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="J10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
-      <c r="K10" s="2" t="inlineStr">
-        <is>
-          <t>12,69%</t>
-        </is>
-      </c>
-      <c r="L10" s="2" t="inlineStr">
-        <is>
-          <t>13,58%</t>
-        </is>
-      </c>
-      <c r="M10" s="2" t="inlineStr">
-        <is>
-          <t>0,0%</t>
-        </is>
-      </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>5,77%</t>
+          <t>5,81%</t>
         </is>
       </c>
     </row>
@@ -1137,12 +1137,12 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 40,84</t>
+          <t>0,0; 34,83</t>
         </is>
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 33,15</t>
+          <t>5,69; 29,49</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
@@ -1152,17 +1152,17 @@
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 54,14</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 35,37</t>
+          <t>0,0; 43,5</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>6,84; 29,69</t>
+          <t>0,0; 35,42</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
@@ -1172,17 +1172,17 @@
       </c>
       <c r="J11" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0,0; 46,38</t>
         </is>
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>2,98; 28,22</t>
+          <t>3,42; 28,14</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>6,73; 25,17</t>
+          <t>6,65; 24,82</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
@@ -1192,7 +1192,7 @@
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>0,0; 28,75</t>
+          <t>0,0; 24,81</t>
         </is>
       </c>
     </row>
@@ -1209,42 +1209,42 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>14,81%</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
+          <t>10,03%</t>
+        </is>
+      </c>
+      <c r="E12" s="2" t="inlineStr">
+        <is>
+          <t>7,46%</t>
+        </is>
+      </c>
+      <c r="F12" s="2" t="inlineStr">
+        <is>
+          <t>11,16%</t>
+        </is>
+      </c>
+      <c r="G12" s="2" t="inlineStr">
+        <is>
           <t>9,69%</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="H12" s="2" t="inlineStr">
         <is>
           <t>4,32%</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="I12" s="2" t="inlineStr">
         <is>
           <t>0,0%</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr">
-        <is>
-          <t>8,17%</t>
-        </is>
-      </c>
-      <c r="G12" s="2" t="inlineStr">
-        <is>
-          <t>14,81%</t>
-        </is>
-      </c>
-      <c r="H12" s="2" t="inlineStr">
-        <is>
-          <t>10,03%</t>
-        </is>
-      </c>
-      <c r="I12" s="2" t="inlineStr">
-        <is>
-          <t>7,46%</t>
-        </is>
-      </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>10,15%</t>
+          <t>7,51%</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
@@ -1264,7 +1264,7 @@
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>9,33%</t>
+          <t>9,57%</t>
         </is>
       </c>
     </row>
@@ -1277,62 +1277,62 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
-          <t>3,64; 21,26</t>
+          <t>7,39; 24,22</t>
         </is>
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>1,17; 11,81</t>
+          <t>4,76; 17,17</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>1,81; 17,83</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 30,43</t>
+          <t>0,0; 33,93</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>7,67; 25,53</t>
+          <t>3,73; 21,0</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>5,31; 16,95</t>
+          <t>1,18; 11,3</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>1,82; 17,13</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
         <is>
-          <t>0,0; 29,46</t>
+          <t>0,0; 27,68</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>7,71; 20,07</t>
+          <t>7,69; 19,83</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>4,53; 12,98</t>
+          <t>4,57; 12,31</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>1,53; 10,81</t>
+          <t>1,15; 10,88</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>2,53; 24,69</t>
+          <t>3,1; 25,23</t>
         </is>
       </c>
     </row>
@@ -1393,7 +1393,7 @@
       <c r="B1" s="2" t="n"/>
       <c r="C1" s="3" t="inlineStr">
         <is>
-          <t>Niña</t>
+          <t>Niño</t>
         </is>
       </c>
       <c r="D1" s="3" t="n"/>
@@ -1401,7 +1401,7 @@
       <c r="F1" s="3" t="n"/>
       <c r="G1" s="3" t="inlineStr">
         <is>
-          <t>Niño</t>
+          <t>Niña</t>
         </is>
       </c>
       <c r="H1" s="3" t="n"/>
@@ -1524,27 +1524,27 @@
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I4" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J4" s="2" t="inlineStr">
+        <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J4" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K4" s="2" t="inlineStr">
@@ -1592,7 +1592,7 @@
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>0</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -1612,7 +1612,7 @@
       </c>
       <c r="J5" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>308</t>
         </is>
       </c>
       <c r="K5" s="2" t="inlineStr">
@@ -1632,7 +1632,7 @@
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>408</t>
+          <t>308</t>
         </is>
       </c>
     </row>
@@ -1660,7 +1660,7 @@
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>0; 758</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -1680,7 +1680,7 @@
       </c>
       <c r="J6" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 566</t>
         </is>
       </c>
       <c r="K6" s="2" t="inlineStr">
@@ -1700,7 +1700,7 @@
       </c>
       <c r="N6" s="2" t="inlineStr">
         <is>
-          <t>0; 1629</t>
+          <t>0; 1374</t>
         </is>
       </c>
     </row>
@@ -1717,19 +1717,19 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="E7" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E7" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -1737,17 +1737,17 @@
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>6</t>
+          <t>2</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1785,37 +1785,37 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>4201</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
+          <t>2162</t>
+        </is>
+      </c>
+      <c r="E8" s="2" t="inlineStr">
+        <is>
+          <t>1611</t>
+        </is>
+      </c>
+      <c r="F8" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" s="2" t="inlineStr">
+        <is>
           <t>1292</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F8" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" s="2" t="inlineStr">
-        <is>
-          <t>4201</t>
-        </is>
-      </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>2162</t>
+          <t>0</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>1611</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
-          <t>0; 4659</t>
+          <t>1932; 7624</t>
         </is>
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>677; 5792</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 4688</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
@@ -1873,17 +1873,17 @@
       </c>
       <c r="G9" s="2" t="inlineStr">
         <is>
-          <t>1973; 7602</t>
+          <t>0; 4138</t>
         </is>
       </c>
       <c r="H9" s="2" t="inlineStr">
         <is>
-          <t>675; 6006</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="I9" s="2" t="inlineStr">
         <is>
-          <t>0; 4646</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J9" s="2" t="inlineStr">
@@ -1893,17 +1893,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>2478; 9555</t>
+          <t>2680; 9476</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>671; 5869</t>
+          <t>671; 5791</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>0; 5464</t>
+          <t>0; 4694</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -1925,42 +1925,42 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="E10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="F10" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G10" s="2" t="inlineStr">
+        <is>
           <t>1</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="H10" s="2" t="inlineStr">
         <is>
           <t>1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F10" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H10" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
         <is>
-          <t>2</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K10" s="2" t="inlineStr">
@@ -1993,62 +1993,62 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>1224</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
+          <t>1718</t>
+        </is>
+      </c>
+      <c r="E11" s="2" t="inlineStr">
+        <is>
+          <t>1429</t>
+        </is>
+      </c>
+      <c r="F11" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="G11" s="2" t="inlineStr">
+        <is>
           <t>806</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="H11" s="2" t="inlineStr">
         <is>
           <t>930</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F11" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G11" s="2" t="inlineStr">
-        <is>
-          <t>1224</t>
-        </is>
-      </c>
-      <c r="H11" s="2" t="inlineStr">
-        <is>
-          <t>1718</t>
-        </is>
-      </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="K11" s="2" t="inlineStr">
+        <is>
+          <t>2030</t>
+        </is>
+      </c>
+      <c r="L11" s="2" t="inlineStr">
+        <is>
+          <t>2648</t>
+        </is>
+      </c>
+      <c r="M11" s="2" t="inlineStr">
+        <is>
           <t>1429</t>
         </is>
       </c>
-      <c r="J11" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="K11" s="2" t="inlineStr">
-        <is>
-          <t>2030</t>
-        </is>
-      </c>
-      <c r="L11" s="2" t="inlineStr">
-        <is>
-          <t>2648</t>
-        </is>
-      </c>
-      <c r="M11" s="2" t="inlineStr">
-        <is>
-          <t>1429</t>
-        </is>
-      </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>2439</t>
+          <t>2483</t>
         </is>
       </c>
     </row>
@@ -2061,62 +2061,62 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
-          <t>0; 3191</t>
+          <t>0; 3378</t>
         </is>
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>0; 4347</t>
+          <t>0; 4968</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3750</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 5689</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
         <is>
-          <t>0; 3813</t>
+          <t>0; 3741</t>
         </is>
       </c>
       <c r="H12" s="2" t="inlineStr">
         <is>
-          <t>0; 5299</t>
+          <t>0; 4309</t>
         </is>
       </c>
       <c r="I12" s="2" t="inlineStr">
         <is>
-          <t>0; 4312</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J12" s="2" t="inlineStr">
         <is>
-          <t>0; 5959</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>524; 5275</t>
+          <t>530; 5350</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>589; 6316</t>
+          <t>621; 6931</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>0; 4438</t>
+          <t>0; 5144</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
         <is>
-          <t>0; 6338</t>
+          <t>0; 7026</t>
         </is>
       </c>
     </row>
@@ -2138,37 +2138,37 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="E13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G13" s="2" t="inlineStr">
+        <is>
           <t>2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" s="2" t="inlineStr">
+      <c r="H13" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I13" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" s="2" t="inlineStr">
         <is>
           <t>1</t>
-        </is>
-      </c>
-      <c r="G13" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="H13" s="2" t="inlineStr">
-        <is>
-          <t>6</t>
-        </is>
-      </c>
-      <c r="I13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
         </is>
       </c>
       <c r="K13" s="2" t="inlineStr">
@@ -2201,34 +2201,34 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>1466</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
+          <t>3479</t>
+        </is>
+      </c>
+      <c r="E14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" s="2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G14" s="2" t="inlineStr">
+        <is>
           <t>1324</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="H14" s="2" t="inlineStr">
         <is>
           <t>1306</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" s="2" t="inlineStr">
-        <is>
-          <t>994</t>
-        </is>
-      </c>
-      <c r="G14" s="2" t="inlineStr">
-        <is>
-          <t>1466</t>
-        </is>
-      </c>
-      <c r="H14" s="2" t="inlineStr">
-        <is>
-          <t>3479</t>
-        </is>
-      </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
           <t>0</t>
@@ -2236,7 +2236,7 @@
       </c>
       <c r="J14" s="2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>983</t>
         </is>
       </c>
       <c r="K14" s="2" t="inlineStr">
@@ -2256,7 +2256,7 @@
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>994</t>
+          <t>983</t>
         </is>
       </c>
     </row>
@@ -2269,12 +2269,12 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
-          <t>0; 3928</t>
+          <t>0; 4308</t>
         </is>
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>0; 3896</t>
+          <t>1336; 6922</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
@@ -2284,17 +2284,17 @@
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>0; 4222</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
         <is>
-          <t>0; 4375</t>
+          <t>0; 4184</t>
         </is>
       </c>
       <c r="H15" s="2" t="inlineStr">
         <is>
-          <t>1606; 6968</t>
+          <t>0; 4163</t>
         </is>
       </c>
       <c r="I15" s="2" t="inlineStr">
@@ -2304,17 +2304,17 @@
       </c>
       <c r="J15" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>0; 3742</t>
         </is>
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>656; 6205</t>
+          <t>753; 6188</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>2370; 8868</t>
+          <t>2341; 8743</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
@@ -2324,7 +2324,7 @@
       </c>
       <c r="N15" s="2" t="inlineStr">
         <is>
-          <t>0; 4954</t>
+          <t>0; 4194</t>
         </is>
       </c>
     </row>
@@ -2341,37 +2341,37 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
+          <t>11</t>
+        </is>
+      </c>
+      <c r="E16" s="2" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="F16" s="2" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="G16" s="2" t="inlineStr">
+        <is>
           <t>5</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="H16" s="2" t="inlineStr">
         <is>
           <t>3</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" s="2" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="G16" s="2" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H16" s="2" t="inlineStr">
-        <is>
-          <t>11</t>
-        </is>
-      </c>
       <c r="I16" s="2" t="inlineStr">
         <is>
-          <t>4</t>
+          <t>0</t>
         </is>
       </c>
       <c r="J16" s="2" t="inlineStr">
@@ -2409,62 +2409,62 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>6890</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
+          <t>7359</t>
+        </is>
+      </c>
+      <c r="E17" s="2" t="inlineStr">
+        <is>
+          <t>3040</t>
+        </is>
+      </c>
+      <c r="F17" s="2" t="inlineStr">
+        <is>
+          <t>2483</t>
+        </is>
+      </c>
+      <c r="G17" s="2" t="inlineStr">
+        <is>
           <t>3422</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="H17" s="2" t="inlineStr">
         <is>
           <t>2236</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" s="2" t="inlineStr">
-        <is>
-          <t>1402</t>
-        </is>
-      </c>
-      <c r="G17" s="2" t="inlineStr">
-        <is>
-          <t>6890</t>
-        </is>
-      </c>
-      <c r="H17" s="2" t="inlineStr">
-        <is>
-          <t>7359</t>
-        </is>
-      </c>
       <c r="I17" s="2" t="inlineStr">
         <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J17" s="2" t="inlineStr">
+        <is>
+          <t>1291</t>
+        </is>
+      </c>
+      <c r="K17" s="2" t="inlineStr">
+        <is>
+          <t>10312</t>
+        </is>
+      </c>
+      <c r="L17" s="2" t="inlineStr">
+        <is>
+          <t>9595</t>
+        </is>
+      </c>
+      <c r="M17" s="2" t="inlineStr">
+        <is>
           <t>3040</t>
         </is>
       </c>
-      <c r="J17" s="2" t="inlineStr">
-        <is>
-          <t>2439</t>
-        </is>
-      </c>
-      <c r="K17" s="2" t="inlineStr">
-        <is>
-          <t>10312</t>
-        </is>
-      </c>
-      <c r="L17" s="2" t="inlineStr">
-        <is>
-          <t>9595</t>
-        </is>
-      </c>
-      <c r="M17" s="2" t="inlineStr">
-        <is>
-          <t>3040</t>
-        </is>
-      </c>
       <c r="N17" s="2" t="inlineStr">
         <is>
-          <t>3841</t>
+          <t>3774</t>
         </is>
       </c>
     </row>
@@ -2477,62 +2477,62 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
-          <t>1284; 7505</t>
+          <t>3440; 11266</t>
         </is>
       </c>
       <c r="D18" s="2" t="inlineStr">
         <is>
-          <t>607; 6107</t>
+          <t>3493; 12598</t>
         </is>
       </c>
       <c r="E18" s="2" t="inlineStr">
         <is>
-          <t>—; —</t>
+          <t>739; 7259</t>
         </is>
       </c>
       <c r="F18" s="2" t="inlineStr">
         <is>
-          <t>0; 5219</t>
+          <t>0; 7549</t>
         </is>
       </c>
       <c r="G18" s="2" t="inlineStr">
         <is>
-          <t>3566; 11877</t>
+          <t>1317; 7413</t>
         </is>
       </c>
       <c r="H18" s="2" t="inlineStr">
         <is>
-          <t>3899; 12435</t>
+          <t>611; 5845</t>
         </is>
       </c>
       <c r="I18" s="2" t="inlineStr">
         <is>
-          <t>741; 6975</t>
+          <t>—; —</t>
         </is>
       </c>
       <c r="J18" s="2" t="inlineStr">
         <is>
-          <t>0; 7081</t>
+          <t>0; 4756</t>
         </is>
       </c>
       <c r="K18" s="2" t="inlineStr">
         <is>
-          <t>6305; 16421</t>
+          <t>6291; 16223</t>
         </is>
       </c>
       <c r="L18" s="2" t="inlineStr">
         <is>
-          <t>5667; 16233</t>
+          <t>5717; 15402</t>
         </is>
       </c>
       <c r="M18" s="2" t="inlineStr">
         <is>
-          <t>980; 6928</t>
+          <t>737; 6970</t>
         </is>
       </c>
       <c r="N18" s="2" t="inlineStr">
         <is>
-          <t>1042; 10170</t>
+          <t>1223; 9950</t>
         </is>
       </c>
     </row>
